--- a/data/手塚カードゲーム_v7_v1.2.xlsx
+++ b/data/手塚カードゲーム_v7_v1.2.xlsx
@@ -1021,7 +1021,7 @@
     <row r="45">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t>・一部のキャラはキーワード「盾持ち」「守り手」を持つ（→H）。</t>
+          <t>・一部のキャラはキーワード「盾持ち」「守り手」「貫通」を持つ（→H）。</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="F132" s="0" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I132" s="0" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="F133" s="0" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I133" s="0" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="F134" s="0" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I134" s="0" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         </is>
       </c>
       <c r="F135" s="0" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I135" s="0" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="F136" s="0" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I136" s="0" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="F137" s="0" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I137" s="0" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         </is>
       </c>
       <c r="F138" s="0" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I138" s="0" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="F139" s="0" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I139" s="0" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         </is>
       </c>
       <c r="F140" s="0" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I140" s="0" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         </is>
       </c>
       <c r="F141" s="0" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I141" s="0" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         </is>
       </c>
       <c r="F142" s="0" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I142" s="0" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="F143" s="0" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I143" s="0" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="F144" s="0" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I144" s="0" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="F145" s="0" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I145" s="0" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         </is>
       </c>
       <c r="F146" s="0" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I146" s="0" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="F147" s="0" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I147" s="0" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="F148" s="0" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I148" s="0" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="F149" s="0" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I149" s="0" t="inlineStr">
         <is>

--- a/data/手塚カードゲーム_v7_v1.2.xlsx
+++ b/data/手塚カードゲーム_v7_v1.2.xlsx
@@ -1297,7 +1297,7 @@
     <row r="89">
       <c r="A89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">　- 盾持ち・守り手は代替判定でも有効(攻撃力・ダイスに関係なく攻撃を完全に止める)。ただし貫通を持つアタッカーには無効。</t>
+          <t xml:space="preserve">　- 盾持ち・守り手は代替判定でも有効(攻撃力・ダイスに関係なく攻撃を完全に止める)。</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
     <row r="93">
       <c r="A93" s="0" t="inlineStr">
         <is>
-          <t>・キーワード「貫通」(2026-06-07追加):攻撃時、相手の盾持ち・守り手の「完全に止める」防御を無視し、通常の攻撃力比べに持ち込む(勝てば突破して得点)。代替判定(PG-001〜005)下でも盾無視は有効。</t>
+          <t>・キーワード「貫通」:このカードが攻撃した時、ブロックしているキャラの攻撃力を上回っていた場合、ブロッカーを没案へ送り、このカードを原稿ゾーンへ送る(得点)。※基本戦闘(突破得点)と同じ挙動。盾持ち/守り手の完全ブロックは貫通でも止められる。</t>
         </is>
       </c>
     </row>
